--- a/Dataset/IT/xlsx/ITAMed_complete.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_complete.xlsx
@@ -25398,7 +25398,7 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Ossigenoterapia In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 1 Prova generale del 22/09/2020</t>
+          <t>Ossigenoterapia</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>Colestiramina In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 2 Prova generale del 22/09/2020</t>
+          <t>Colestiramina</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Infusione fattore VIII In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 3 Prova generale del 22/09/2020</t>
+          <t>Infusione fattore VIII</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Esofagogastroduodenoscopia In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 4 Prova generale del 22/09/2020</t>
+          <t>Esofagogastroduodenoscopia</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Candidosi In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 5 Prova generale del 22/09/2020</t>
+          <t>Candidosi</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Ipotiroidismo primitivo In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 6 Prova generale del 22/09/2020</t>
+          <t>Ipotiroidismo primitivo</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Infliximab In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 7 Prova generale del 22/09/2020</t>
+          <t>Infliximab</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Ritmo sinusale con emiblocco fascicolare In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 8 Prova generale del 22/09/2020</t>
+          <t>Ritmo sinusale con emiblocco fascicolare</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>L'ipertensione arteriosa rappresenta un fattore di rischio per lo scompenso cardiaco In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 9 Prova generale del 22/09/2020</t>
+          <t>L'ipertensione arteriosa rappresenta un fattore di rischio per lo scompenso cardiaco</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Cefalea In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 10 Prova generale del 22/09/2020</t>
+          <t>Cefalea</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Salazopirina In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 11 Prova generale del 22/09/2020</t>
+          <t>Salazopirina</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>RM cerebrale In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 12 Prova generale del 22/09/2020</t>
+          <t>RM cerebrale</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>Dosaggio calprotectina fecale In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 13 Prova generale del 22/09/2020</t>
+          <t>Dosaggio calprotectina fecale</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>Malaria In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 14 Prova generale del 22/09/2020</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -29014,7 +29014,7 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>&gt;1 e &lt;= 5 mm In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 15 Prova generale del 22/09/2020</t>
+          <t>&gt;1 e &lt;= 5 mm</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>Colectomia totale con ileostomia In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 16 Prova generale del 22/09/2020</t>
+          <t>Colectomia totale con ileostomia</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Una vena, un'arteria e chorion In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 17 Prova generale del 22/09/2020</t>
+          <t>Una vena, un'arteria e chorion</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -29884,7 +29884,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Zygote Intra Fallopian Transfer In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 18 Prova generale del 22/09/2020</t>
+          <t>Zygote Intra Fallopian Transfer</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>Cisti ossea In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 19 Prova generale del 22/09/2020</t>
+          <t>Cisti ossea</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Tutte le altre risposte sono corrette In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 20 Prova generale del 22/09/2020</t>
+          <t>Tutte le altre risposte sono corrette</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
@@ -30474,7 +30474,7 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Emorragia subaracnoidea In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 21 Prova generale del 22/09/2020</t>
+          <t>Emorragia subaracnoidea</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -30716,7 +30716,7 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>Cure termali In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 22 Prova generale del 22/09/2020</t>
+          <t>Cure termali</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -31006,7 +31006,7 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Abolizione del fumo In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 23 Prova generale del 22/09/2020</t>
+          <t>Abolizione del fumo</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Epatica In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 24 Prova generale del 22/09/2020</t>
+          <t>Epatica</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>Ecografia con mezzo di contrasto In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 25 Prova generale del 22/09/2020</t>
+          <t>Ecografia con mezzo di contrasto</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
@@ -31644,7 +31644,7 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Immagine A: sequenza T2; Immagine B: sequenza T2 con mezzo di contrasto In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 26 Prova generale del 22/09/2020</t>
+          <t>Immagine A: sequenza T2; Immagine B: sequenza T2 con mezzo di contrasto</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
@@ -31838,7 +31838,7 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Sovraslivellamento dell'emidiaframma sinistro In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 27 Prova generale del 22/09/2020</t>
+          <t>Sovraslivellamento dell'emidiaframma sinistro</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
@@ -32070,7 +32070,7 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Esecuzione TC addome con mezzo di contrasto per valutare eziologia dell'insufficienza renale In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 28 Prova generale del 22/09/2020</t>
+          <t>Esecuzione TC addome con mezzo di contrasto per valutare eziologia dell'insufficienza renale</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -32302,7 +32302,7 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>Isoprenalina In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 29 Prova generale del 22/09/2020</t>
+          <t>Isoprenalina</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>Nessuna delle altre risposte è corretta In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 30 Prova generale del 22/09/2020</t>
+          <t>Nessuna delle altre risposte è corretta</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
@@ -32882,7 +32882,7 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>La vaccinazione anti difterite-tetano-pertosse non è più obbligatoria In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 31 Prova generale del 22/09/2020</t>
+          <t>La vaccinazione anti difterite-tetano-pertosse non è più obbligatoria</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>In merito all'interruzione volontaria di gravidanza nei primi 90 giorni dal concepimento (legge 194/1978) In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 32 Prova generale del 22/09/2020</t>
+          <t>In merito all'interruzione volontaria di gravidanza nei primi 90 giorni dal concepimento (legge 194/1978)</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
@@ -33288,7 +33288,7 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Media e mediana coincidono In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 33</t>
+          <t>Media e mediana coincidono</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_complete.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_complete.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Farmacologia e Tossicologia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
+          <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pediatria; Chirurgia Generale</t>
+          <t>Pediatria; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Medicina del Lavoro</t>
+          <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Gastroenterologia</t>
+          <t>Gastroenterologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Medicina Interna</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Endocrinologia; Nefrologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Anestesia e Rianimazione</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Oncologia; Gastroenterologia</t>
+          <t>Gastroenterologia; Oncologia</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Oncologia; Farmacologia e Tossicologia</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Endocrinologia; Pediatria</t>
+          <t>Pediatria; Endocrinologia</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Endocrinologia; Pediatria</t>
+          <t>Pediatria</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pediatria; Urologia</t>
+          <t>Pediatria; Nefrologia</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Pediatria; Urologia</t>
+          <t>Pediatria; Malattie Infettive</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Psichiatria; Farmacologia e Tossicologia</t>
+          <t>Psichiatria</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Urologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Urologia; Farmacologia e Tossicologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Malattie Infettive</t>
+          <t>Malattie Infettive; Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Endocrinologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Medicina Legale</t>
+          <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Nefrologia</t>
+          <t>Nefrologia; Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Farmacologia e Tossicologia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Endocrinologia; Nefrologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Nefrologia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Pneumologia e Chirurgia Toracica</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Nefrologia; Endocrinologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Ginecologia e Ostetricia</t>
+          <t>Dermatologia e Venereologia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Nefrologia; Farmacologia e Tossicologia</t>
+          <t>Nefrologia</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Nefrologia; Immunologia e Reumatologia</t>
+          <t>Immunologia e Reumatologia; Nefrologia</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Oncologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Oftalmologia; Pediatria</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Oncologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Pediatria</t>
+          <t>Otorinolaringoiatria; Pediatria</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Oncologia</t>
+          <t>Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Anestesia e Rianimazione</t>
+          <t>Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Medicina Legale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Anestesia e Rianimazione</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Chirurgia Generale</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Chirurgia Generale</t>
+          <t>Chirurgia Generale; Malattie Infettive</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Oncologia; Gastroenterologia</t>
+          <t>Gastroenterologia; Oncologia</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Chirurgia Generale</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Genetica Medica</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Pneumologia e Chirurgia Toracica</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Ematologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Ematologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica</t>
+          <t>Malattie Infettive; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Ematologia; Ginecologia e Ostetricia</t>
+          <t>Ginecologia e Ostetricia; Ematologia</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -22072,7 +22072,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Malattie Infettive</t>
+          <t>Malattie Infettive; Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -22662,7 +22662,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -22778,7 +22778,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Pediatria; Psichiatria</t>
+          <t>Pediatria</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Pediatria</t>
+          <t>Pediatria; Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Pediatria</t>
+          <t>Pediatria; Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Pediatria</t>
+          <t>Pediatria; Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Genetica Medica; Pediatria</t>
+          <t>Pediatria; Genetica Medica</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Nefrologia; Pediatria</t>
+          <t>Pediatria; Nefrologia</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Ematologia; Pediatria</t>
+          <t>Genetica Medica</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Endocrinologia; Pediatria</t>
+          <t>Pediatria; Endocrinologia</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -24944,7 +24944,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Igiene, Epidemiologia e Statistica</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Ematologia; Farmacologia e Tossicologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Ematologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -25988,7 +25988,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Urologia; Farmacologia e Tossicologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -26162,7 +26162,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Oncologia; Ortopedia e Traumatologia</t>
+          <t>Ematologia; Pediatria</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Malattie Infettive</t>
+          <t>Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Ematologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -27216,7 +27216,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -27922,7 +27922,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Farmacologia e Tossicologia</t>
+          <t>Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -27980,7 +27980,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Ematologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Oftalmologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Pediatria; Oncologia</t>
+          <t>Pediatria; Ematologia</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>Ematologia; Pediatria</t>
+          <t>Pediatria; Ematologia</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -28908,7 +28908,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Anestesia e Rianimazione</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Endocrinologia</t>
+          <t>Endocrinologia; Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Farmacologia e Tossicologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -30784,7 +30784,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Genetica Medica; Otorinolaringoiatria</t>
+          <t>Genetica Medica</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -30842,7 +30842,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Otorinolaringoiatria; Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Neurologia e Neurochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Malattie Infettive</t>
+          <t>Malattie Infettive; Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -31596,7 +31596,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Urologia</t>
+          <t>Urologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -31790,7 +31790,7 @@
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -32080,7 +32080,7 @@
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Nefrologia; Farmacologia e Tossicologia</t>
+          <t>Nefrologia</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -32196,7 +32196,7 @@
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Nefrologia</t>
+          <t>Nefrologia; Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Malattie Infettive</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
@@ -33414,7 +33414,7 @@
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Gastroenterologia</t>
+          <t>Gastroenterologia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Chirurgia Generale</t>
+          <t>Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
@@ -34700,7 +34700,7 @@
       </c>
       <c r="K585" t="inlineStr">
         <is>
-          <t>Ematologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="K588" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
@@ -34990,7 +34990,7 @@
       </c>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Nutrizione Clinica; Gastroenterologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>Genetica Medica; Oncologia</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
@@ -35706,7 +35706,7 @@
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Malattie Infettive</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
@@ -36634,7 +36634,7 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Pediatria</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
@@ -37330,7 +37330,7 @@
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
@@ -38026,7 +38026,7 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Igiene, Epidemiologia e Statistica</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Ginecologia e Ostetricia</t>
+          <t>Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>Urologia; Oncologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -38664,7 +38664,7 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Oftalmologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Endocrinologia</t>
+          <t>Otorinolaringoiatria; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -39196,7 +39196,7 @@
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Chirurgia Generale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -39428,7 +39428,7 @@
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Anestesia e Rianimazione</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
@@ -40376,7 +40376,7 @@
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L682" t="inlineStr">
@@ -40608,7 +40608,7 @@
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -40898,7 +40898,7 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
@@ -40956,7 +40956,7 @@
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L692" t="inlineStr">
@@ -41130,7 +41130,7 @@
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Medicina Legale; Igiene, Epidemiologia e Statistica</t>
+          <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -41246,7 +41246,7 @@
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>Medicina del Lavoro; Oncologia</t>
+          <t>Medicina del Lavoro</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -41304,7 +41304,7 @@
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Medicina del Lavoro</t>
+          <t>Medicina del Lavoro; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L698" t="inlineStr">
@@ -41420,7 +41420,7 @@
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Medicina Legale; Ginecologia e Ostetricia</t>
+          <t>Medicina Legale</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -41710,7 +41710,7 @@
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Oncologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
@@ -43344,7 +43344,7 @@
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
@@ -43402,7 +43402,7 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Oncologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Oncologia</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -44098,7 +44098,7 @@
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>Nefrologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Nefrologia</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
@@ -44272,7 +44272,7 @@
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Nefrologia</t>
+          <t>Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L749" t="inlineStr">
@@ -44446,7 +44446,7 @@
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>Endocrinologia; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Endocrinologia</t>
         </is>
       </c>
       <c r="L752" t="inlineStr">
@@ -44504,7 +44504,7 @@
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Genetica Medica</t>
+          <t>Neurologia e Neurochirurgia; Pediatria</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
@@ -44678,7 +44678,7 @@
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>Pediatria; Chirurgia Generale</t>
+          <t>Chirurgia Generale; Pediatria</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>Nefrologia; Genetica Medica</t>
+          <t>Nefrologia</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
@@ -45780,7 +45780,7 @@
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Oncologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L775" t="inlineStr">
@@ -46370,7 +46370,7 @@
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
@@ -46796,7 +46796,7 @@
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Neurologia e Neurochirurgia</t>
+          <t>Ortopedia e Traumatologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L801" t="inlineStr">
@@ -47434,7 +47434,7 @@
       </c>
       <c r="K803" t="inlineStr">
         <is>
-          <t>Chirurgia Generale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L803" t="inlineStr">
@@ -47666,7 +47666,7 @@
       </c>
       <c r="K807" t="inlineStr">
         <is>
-          <t>Ematologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L807" t="inlineStr">
@@ -47782,7 +47782,7 @@
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Immunologia e Reumatologia</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
@@ -47898,7 +47898,7 @@
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Nutrizione Clinica</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
@@ -48014,7 +48014,7 @@
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Chirurgia Generale</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L813" t="inlineStr">
@@ -48246,7 +48246,7 @@
       </c>
       <c r="K817" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Medicina Legale</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L817" t="inlineStr">
@@ -48304,7 +48304,7 @@
       </c>
       <c r="K818" t="inlineStr">
         <is>
-          <t>Oncologia; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Oncologia</t>
         </is>
       </c>
       <c r="L818" t="inlineStr">
@@ -48362,7 +48362,7 @@
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
+          <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L819" t="inlineStr">
@@ -48768,7 +48768,7 @@
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
@@ -48942,7 +48942,7 @@
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>Oncologia; Genetica Medica</t>
+          <t>Genetica Medica; Oncologia</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
@@ -49116,7 +49116,7 @@
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
@@ -49290,7 +49290,7 @@
       </c>
       <c r="K835" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Malattie Infettive</t>
+          <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L835" t="inlineStr">
@@ -49348,7 +49348,7 @@
       </c>
       <c r="K836" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Malattie Infettive</t>
+          <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L836" t="inlineStr">
@@ -49406,7 +49406,7 @@
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t>Medicina del Lavoro; Pneumologia e Chirurgia Toracica</t>
+          <t>Medicina del Lavoro</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
@@ -49986,7 +49986,7 @@
       </c>
       <c r="K847" t="inlineStr">
         <is>
-          <t>Genetica Medica; Oncologia</t>
+          <t>Oncologia; Genetica Medica</t>
         </is>
       </c>
       <c r="L847" t="inlineStr">
@@ -50160,7 +50160,7 @@
       </c>
       <c r="K850" t="inlineStr">
         <is>
-          <t>Oftalmologia; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Oftalmologia</t>
         </is>
       </c>
       <c r="L850" t="inlineStr">
@@ -50392,7 +50392,7 @@
       </c>
       <c r="K854" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Oncologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
@@ -50450,7 +50450,7 @@
       </c>
       <c r="K855" t="inlineStr">
         <is>
-          <t>Endocrinologia; Genetica Medica</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L855" t="inlineStr">
@@ -50934,7 +50934,7 @@
       </c>
       <c r="K863" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Chirurgia Generale</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L863" t="inlineStr">
@@ -51108,7 +51108,7 @@
       </c>
       <c r="K866" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Endocrinologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L866" t="inlineStr">
@@ -51688,7 +51688,7 @@
       </c>
       <c r="K876" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L876" t="inlineStr">
@@ -52442,7 +52442,7 @@
       </c>
       <c r="K889" t="inlineStr">
         <is>
-          <t>Pediatria; Malattie Infettive</t>
+          <t>Malattie Infettive; Pediatria</t>
         </is>
       </c>
       <c r="L889" t="inlineStr">
@@ -52626,7 +52626,7 @@
       </c>
       <c r="K892" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Farmacologia e Tossicologia</t>
+          <t>Farmacologia e Tossicologia; Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L892" t="inlineStr">
@@ -52878,7 +52878,7 @@
       </c>
       <c r="K896" t="inlineStr">
         <is>
-          <t>Endocrinologia; Oncologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L896" t="inlineStr">
@@ -53168,7 +53168,7 @@
       </c>
       <c r="K901" t="inlineStr">
         <is>
-          <t>Psichiatria; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Psichiatria</t>
         </is>
       </c>
       <c r="L901" t="inlineStr">
@@ -53758,7 +53758,7 @@
       </c>
       <c r="K911" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Farmacologia e Tossicologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L911" t="inlineStr">
@@ -54048,7 +54048,7 @@
       </c>
       <c r="K916" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L916" t="inlineStr">
@@ -54106,7 +54106,7 @@
       </c>
       <c r="K917" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Anestesia e Rianimazione</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L917" t="inlineStr">
@@ -54164,7 +54164,7 @@
       </c>
       <c r="K918" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L918" t="inlineStr">
@@ -54812,7 +54812,7 @@
       </c>
       <c r="K929" t="inlineStr">
         <is>
-          <t>Oncologia; Ematologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L929" t="inlineStr">
@@ -55566,7 +55566,7 @@
       </c>
       <c r="K942" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Psichiatria</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L942" t="inlineStr">
@@ -55856,7 +55856,7 @@
       </c>
       <c r="K947" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L947" t="inlineStr">
@@ -56176,7 +56176,7 @@
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L952" t="inlineStr">
@@ -56350,7 +56350,7 @@
       </c>
       <c r="K955" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L955" t="inlineStr">
@@ -56524,7 +56524,7 @@
       </c>
       <c r="K958" t="inlineStr">
         <is>
-          <t>Genetica Medica; Pediatria</t>
+          <t>Pediatria; Malattie Infettive</t>
         </is>
       </c>
       <c r="L958" t="inlineStr">
@@ -56698,7 +56698,7 @@
       </c>
       <c r="K961" t="inlineStr">
         <is>
-          <t>Medicina Legale</t>
+          <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
         </is>
       </c>
       <c r="L961" t="inlineStr">
@@ -56930,7 +56930,7 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>Medicina Legale; Pediatria</t>
+          <t>Medicina Legale</t>
         </is>
       </c>
       <c r="L965" t="inlineStr">
@@ -57162,7 +57162,7 @@
       </c>
       <c r="K969" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L969" t="inlineStr">
@@ -57336,7 +57336,7 @@
       </c>
       <c r="K972" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Urologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L972" t="inlineStr">
@@ -57520,7 +57520,7 @@
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L975" t="inlineStr">
@@ -57578,7 +57578,7 @@
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L976" t="inlineStr">
@@ -57694,7 +57694,7 @@
       </c>
       <c r="K978" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Pneumologia e Chirurgia Toracica</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L978" t="inlineStr">
@@ -58622,7 +58622,7 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>Chirurgia Generale</t>
+          <t>Dermatologia e Venereologia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L994" t="inlineStr">
@@ -58796,7 +58796,7 @@
       </c>
       <c r="K997" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Chirurgia Generale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L997" t="inlineStr">
@@ -59086,7 +59086,7 @@
       </c>
       <c r="K1002" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L1002" t="inlineStr">
@@ -59144,7 +59144,7 @@
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L1003" t="inlineStr">
@@ -59608,7 +59608,7 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L1011" t="inlineStr">
@@ -59782,7 +59782,7 @@
       </c>
       <c r="K1014" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Chirurgia Generale</t>
+          <t>Chirurgia Generale; Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L1014" t="inlineStr">
@@ -60072,7 +60072,7 @@
       </c>
       <c r="K1019" t="inlineStr">
         <is>
-          <t>Urologia; Oncologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L1019" t="inlineStr">
@@ -60556,7 +60556,7 @@
       </c>
       <c r="K1027" t="inlineStr">
         <is>
-          <t>Nefrologia; Ematologia</t>
+          <t>Ematologia; Nefrologia</t>
         </is>
       </c>
       <c r="L1027" t="inlineStr">
@@ -60846,7 +60846,7 @@
       </c>
       <c r="K1032" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Ematologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L1032" t="inlineStr">
@@ -60962,7 +60962,7 @@
       </c>
       <c r="K1034" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L1034" t="inlineStr">
@@ -61078,7 +61078,7 @@
       </c>
       <c r="K1036" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Pediatria</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L1036" t="inlineStr">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="K1050" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L1050" t="inlineStr">
@@ -62490,7 +62490,7 @@
       </c>
       <c r="K1060" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L1060" t="inlineStr">
@@ -63012,7 +63012,7 @@
       </c>
       <c r="K1069" t="inlineStr">
         <is>
-          <t>Urologia; Oncologia</t>
+          <t>Oncologia; Urologia</t>
         </is>
       </c>
       <c r="L1069" t="inlineStr">
@@ -63070,7 +63070,7 @@
       </c>
       <c r="K1070" t="inlineStr">
         <is>
-          <t>Oncologia; Farmacologia e Tossicologia</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L1070" t="inlineStr">
@@ -63128,7 +63128,7 @@
       </c>
       <c r="K1071" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Pediatria</t>
+          <t>Oftalmologia; Pediatria</t>
         </is>
       </c>
       <c r="L1071" t="inlineStr">
@@ -63360,7 +63360,7 @@
       </c>
       <c r="K1075" t="inlineStr">
         <is>
-          <t>Genetica Medica; Pediatria</t>
+          <t>Genetica Medica; Endocrinologia</t>
         </is>
       </c>
       <c r="L1075" t="inlineStr">
@@ -63418,7 +63418,7 @@
       </c>
       <c r="K1076" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Pediatria</t>
+          <t>Pediatria; Gastroenterologia</t>
         </is>
       </c>
       <c r="L1076" t="inlineStr">
@@ -63534,7 +63534,7 @@
       </c>
       <c r="K1078" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Pediatria</t>
+          <t>Pediatria; Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L1078" t="inlineStr">
@@ -63766,7 +63766,7 @@
       </c>
       <c r="K1082" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Ortopedia e Traumatologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L1082" t="inlineStr">
@@ -63940,7 +63940,7 @@
       </c>
       <c r="K1085" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Oncologia</t>
+          <t>Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L1085" t="inlineStr">
@@ -63998,7 +63998,7 @@
       </c>
       <c r="K1086" t="inlineStr">
         <is>
-          <t>Oncologia; Dermatologia e Venereologia</t>
+          <t>Dermatologia e Venereologia; Oncologia</t>
         </is>
       </c>
       <c r="L1086" t="inlineStr">
@@ -64346,7 +64346,7 @@
       </c>
       <c r="K1092" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L1092" t="inlineStr">
@@ -64404,7 +64404,7 @@
       </c>
       <c r="K1093" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Ortopedia e Traumatologia</t>
+          <t>Ortopedia e Traumatologia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L1093" t="inlineStr">
@@ -65516,7 +65516,7 @@
       </c>
       <c r="K1112" t="inlineStr">
         <is>
-          <t>Ematologia; Gastroenterologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L1112" t="inlineStr">
@@ -66126,7 +66126,7 @@
       </c>
       <c r="K1122" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Pediatria</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L1122" t="inlineStr">
@@ -66184,7 +66184,7 @@
       </c>
       <c r="K1123" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L1123" t="inlineStr">
@@ -66706,7 +66706,7 @@
       </c>
       <c r="K1132" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L1132" t="inlineStr">
@@ -66938,7 +66938,7 @@
       </c>
       <c r="K1136" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L1136" t="inlineStr">
@@ -67054,7 +67054,7 @@
       </c>
       <c r="K1138" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L1138" t="inlineStr">
@@ -67112,7 +67112,7 @@
       </c>
       <c r="K1139" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L1139" t="inlineStr">
@@ -67228,7 +67228,7 @@
       </c>
       <c r="K1141" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L1141" t="inlineStr">
@@ -67876,7 +67876,7 @@
       </c>
       <c r="K1152" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L1152" t="inlineStr">
@@ -67934,7 +67934,7 @@
       </c>
       <c r="K1153" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L1153" t="inlineStr">
@@ -68370,7 +68370,7 @@
       </c>
       <c r="K1160" t="inlineStr">
         <is>
-          <t>Urologia; Farmacologia e Tossicologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L1160" t="inlineStr">
@@ -68428,7 +68428,7 @@
       </c>
       <c r="K1161" t="inlineStr">
         <is>
-          <t>Urologia; Genetica Medica</t>
+          <t>Urologia; Oncologia</t>
         </is>
       </c>
       <c r="L1161" t="inlineStr">
@@ -69338,7 +69338,7 @@
       </c>
       <c r="K1176" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L1176" t="inlineStr">
@@ -69628,7 +69628,7 @@
       </c>
       <c r="K1181" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Ginecologia e Ostetricia</t>
+          <t>Anestesia e Rianimazione; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L1181" t="inlineStr">
@@ -69754,7 +69754,7 @@
       </c>
       <c r="K1183" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Malattie Infettive</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L1183" t="inlineStr">
@@ -69996,7 +69996,7 @@
       </c>
       <c r="K1187" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L1187" t="inlineStr">
@@ -70112,7 +70112,7 @@
       </c>
       <c r="K1189" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L1189" t="inlineStr">
@@ -70170,7 +70170,7 @@
       </c>
       <c r="K1190" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Ortopedia e Traumatologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L1190" t="inlineStr">
@@ -70228,7 +70228,7 @@
       </c>
       <c r="K1191" t="inlineStr">
         <is>
-          <t>Ematologia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L1191" t="inlineStr">
@@ -71456,7 +71456,7 @@
       </c>
       <c r="K1212" t="inlineStr">
         <is>
-          <t>Genetica Medica; Immunologia e Reumatologia</t>
+          <t>Genetica Medica</t>
         </is>
       </c>
       <c r="L1212" t="inlineStr">
@@ -72742,7 +72742,7 @@
       </c>
       <c r="K1234" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Anestesia e Rianimazione</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L1234" t="inlineStr">
@@ -72974,7 +72974,7 @@
       </c>
       <c r="K1238" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L1238" t="inlineStr">
@@ -73322,7 +73322,7 @@
       </c>
       <c r="K1244" t="inlineStr">
         <is>
-          <t>Medicina del Lavoro; Otorinolaringoiatria</t>
+          <t>Medicina del Lavoro</t>
         </is>
       </c>
       <c r="L1244" t="inlineStr">
@@ -73786,7 +73786,7 @@
       </c>
       <c r="K1252" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Ematologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L1252" t="inlineStr">
@@ -73902,7 +73902,7 @@
       </c>
       <c r="K1254" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L1254" t="inlineStr">
@@ -73960,7 +73960,7 @@
       </c>
       <c r="K1255" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Gastroenterologia</t>
+          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L1255" t="inlineStr">
@@ -74018,7 +74018,7 @@
       </c>
       <c r="K1256" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L1256" t="inlineStr">
@@ -74076,7 +74076,7 @@
       </c>
       <c r="K1257" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L1257" t="inlineStr">
@@ -74260,7 +74260,7 @@
       </c>
       <c r="K1260" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L1260" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_complete.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_complete.xlsx
@@ -40086,7 +40086,7 @@
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>Brain CT Scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="N677" t="inlineStr">
@@ -65952,7 +65952,7 @@
       </c>
       <c r="M1119" t="inlineStr">
         <is>
-          <t>Brain TC scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="N1119" t="inlineStr">
